--- a/data/trans_orig/IP16CS1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16CS1_2023-Edad-trans_orig.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>8082</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1473</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,76%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>477</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4356</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>454</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>61,34%</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>40,97%</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>79,31%</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9886</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12724</t>
+          <t>12765</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14888</t>
+          <t>14968</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21667</t>
+          <t>21648</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>469</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>501</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>384</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>369</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16CS1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16CS1_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4995</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3889</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5308</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>94,1%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>73,27%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3395</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2177</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3745</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>90,65%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>58,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3020</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3278</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>92,13%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>60,61%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6305</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5036</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6686</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>94,3%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>75,32%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>21</t>
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1567</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>41,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>258</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -946,82 +946,82 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1650</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>24,68%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>313</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5308</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5308</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5308</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3745</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>3745</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>3745</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>69,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14,1%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3582</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1473</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5217</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>62,91%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>91,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5720</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>87,29%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4221</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>37,09%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>74,13%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>388</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>415</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>66,08%</t>
         </is>
       </c>
     </row>
@@ -1854,82 +1854,82 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>616</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2434</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>24,84%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>85,54%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>616</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3499</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>36,65%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>5694</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>5694</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>5694</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>8539</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8539</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8539</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1877</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2180</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>86,08%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1877</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2235</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>83,96%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,27 +2159,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>682</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2536,82 +2536,82 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2235</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>16,04%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>303</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>72,91%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2180</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2180</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2180</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>338</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>338</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>338</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>424</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,44 +2796,44 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>67,57%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>1537</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>50,19%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>1883</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>25,69%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>2</t>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>87,06%</t>
         </is>
       </c>
     </row>
@@ -2879,74 +2879,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>721</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1413</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>51,03%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>1537</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>49,81%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>766</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>88,03%</t>
         </is>
       </c>
     </row>
@@ -3105,82 +3105,82 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>407</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>1883</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>24,63%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>407</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>69,02%</t>
         </is>
       </c>
     </row>
@@ -3218,82 +3218,82 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>950</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>935</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>1883</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>49,68%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>950</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>83,32%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>1781</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1781</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1781</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>1413</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>1413</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1413</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>8670</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>6015</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>10400</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>77,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>53,41%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>92,36%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>8048</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>5237</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>10108</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>71,66%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>46,63%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>90,0%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>10803</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12765</t>
+          <t>9153</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>15769</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14968</t>
+          <t>11843</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>18495</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,02%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>3756</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>9,54%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>33,44%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>14,62%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>4932</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>18,8%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>43,91%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>414</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>675</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -3787,82 +3787,82 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>407</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>2576</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>18,87%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>407</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -3900,107 +3900,107 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>318</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>4950</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>14,66%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>36,26%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>311</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>11260</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>11260</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>11260</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>11231</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>11231</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>11231</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>13649</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>13649</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>13649</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>24880</t>
+          <t>21501</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>24880</t>
+          <t>21501</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>24880</t>
+          <t>21501</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
